--- a/Signals.xlsx
+++ b/Signals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Downloads\Apps\Manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDB0DB3-D3CD-428B-A3EE-70077E432A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CC54B6-98FE-4738-938F-F32560BD580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="390" windowWidth="34515" windowHeight="14685" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
+    <workbookView xWindow="14370" yWindow="750" windowWidth="34515" windowHeight="14685" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="116">
   <si>
     <t>View</t>
   </si>
@@ -366,16 +366,25 @@
     <t>Balance_Score</t>
   </si>
   <si>
-    <t>Fib50 Touch, Close Below Box Candle</t>
-  </si>
-  <si>
     <t>Direction</t>
   </si>
   <si>
     <t>VWAP</t>
   </si>
   <si>
-    <t>RSI 70+ risky Ambush Long only Short if Later Close Below Vwap middle even if touch lower and RSI 70+ of this candle</t>
+    <t>Fib38 Touch, Close Below Box Candle</t>
+  </si>
+  <si>
+    <t>Ambush Long , RSI 70+ risky  only Short if Later Close Below Vwap middle even if touch lower and RSI 70+ of this candle</t>
+  </si>
+  <si>
+    <t>Long if 2nd 30 min close above Upper wvap, SL Fib 38, Middle vwap whichever is resonable</t>
+  </si>
+  <si>
+    <t>Ambush Long, C2 VWAP Width % &lt; 0.10 AND C2 breaks first high but closes below first high AND/OR C2 closes below Upper VWAP</t>
+  </si>
+  <si>
+    <t>Long if 30 min close above vwap, Narrow vwap risky always even if second closes above or below</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1001,7 @@
     <col min="3" max="3" width="8.7109375" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="78.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="113.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="132" style="29" customWidth="1"/>
     <col min="7" max="13" width="10" style="30" customWidth="1"/>
     <col min="14" max="15" width="10" style="30" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="15.7109375" style="30" bestFit="1" customWidth="1"/>
@@ -1008,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>49</v>
@@ -1017,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -1118,9 +1127,11 @@
         <v>42</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="G3" s="8">
         <v>22</v>
       </c>
@@ -1167,7 +1178,9 @@
       <c r="E4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="G4" s="8">
         <v>27</v>
       </c>
@@ -1216,7 +1229,9 @@
       <c r="E5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="10"/>
+      <c r="F5" s="10" t="s">
+        <v>115</v>
+      </c>
       <c r="G5" s="12">
         <v>5</v>
       </c>

--- a/Signals.xlsx
+++ b/Signals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Downloads\Apps\Manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CC54B6-98FE-4738-938F-F32560BD580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2775F1-9F94-4E1E-8965-5258583E1560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="750" windowWidth="34515" windowHeight="14685" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
+    <workbookView xWindow="14880" yWindow="225" windowWidth="34515" windowHeight="14685" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="120">
   <si>
     <t>View</t>
   </si>
@@ -385,6 +385,18 @@
   </si>
   <si>
     <t>Long if 30 min close above vwap, Narrow vwap risky always even if second closes above or below</t>
+  </si>
+  <si>
+    <t>If Doji hammer, let 5 min close below middle vwap otherwise ambush, Sl 30 min close above VWAP middle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrow vwap, always worth wait to enter </t>
+  </si>
+  <si>
+    <t>Less data but always worth to see if 5 min show resistance near middle vwap then short</t>
+  </si>
+  <si>
+    <t>Enter when 5 min close below middle vwap</t>
   </si>
 </sst>
 </file>
@@ -3837,7 +3849,9 @@
       <c r="E71" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="G71" s="19">
         <v>18</v>
       </c>
@@ -3884,7 +3898,9 @@
       <c r="E72" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G72" s="19">
         <v>4</v>
       </c>
@@ -3931,7 +3947,9 @@
       <c r="E73" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="G73" s="19">
         <v>2</v>
       </c>
@@ -3976,7 +3994,9 @@
       <c r="E74" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F74" s="5"/>
+      <c r="F74" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G74" s="19">
         <v>9</v>
       </c>

--- a/Signals.xlsx
+++ b/Signals.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Downloads\Apps\Manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harpreetsingh/Downloads/Backtest-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2775F1-9F94-4E1E-8965-5258583E1560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FE9E32-A1F0-FD4A-8F4F-1DE102443DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14880" yWindow="225" windowWidth="34515" windowHeight="14685" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{19F2ECB9-DA0F-44D1-BE0D-B933DAAEA8B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="123">
   <si>
     <t>View</t>
   </si>
@@ -397,6 +397,15 @@
   </si>
   <si>
     <t>Enter when 5 min close below middle vwap</t>
+  </si>
+  <si>
+    <t>Less Data if market is below vwap at 30 close can enter at 5 min close above vwap</t>
+  </si>
+  <si>
+    <t>less data 2nd candle resist from 1st high very risky</t>
+  </si>
+  <si>
+    <t>5 min touch any vwap level and close below first 30 min low</t>
   </si>
 </sst>
 </file>
@@ -1006,22 +1015,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015D4B36-7C06-4EAC-AF4F-111DA5726F93}">
   <dimension ref="A1:Q147"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="78.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="132" style="29" customWidth="1"/>
     <col min="7" max="13" width="10" style="30" customWidth="1"/>
     <col min="14" max="15" width="10" style="30" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="147.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.7109375" style="3"/>
+    <col min="16" max="16" width="15.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="147.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1127,7 +1136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>4</v>
@@ -1176,7 +1185,7 @@
       </c>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>4</v>
@@ -1227,7 +1236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
         <v>4</v>
@@ -1278,7 +1287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="B6" s="14"/>
       <c r="C6" s="32" t="s">
@@ -1301,7 +1310,7 @@
       <c r="P6" s="13"/>
       <c r="Q6" s="17"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
@@ -1317,7 +1326,9 @@
       <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="G7" s="19">
         <v>4</v>
       </c>
@@ -1352,7 +1363,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="9" t="s">
         <v>5</v>
@@ -1366,7 +1377,9 @@
       <c r="E8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="G8" s="19">
         <v>4</v>
       </c>
@@ -1399,7 +1412,7 @@
       </c>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="9" t="s">
         <v>5</v>
@@ -1413,7 +1426,9 @@
       <c r="E9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="G9" s="8">
         <v>3</v>
       </c>
@@ -1446,7 +1461,7 @@
       </c>
       <c r="Q9" s="20"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="15"/>
       <c r="C10" s="32" t="s">
@@ -1469,7 +1484,7 @@
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -1516,7 +1531,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="20"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
         <v>6</v>
@@ -1561,7 +1576,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="20"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
         <v>6</v>
@@ -1606,7 +1621,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="20"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="5" t="s">
         <v>6</v>
@@ -1649,7 +1664,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="20"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
         <v>6</v>
@@ -1694,7 +1709,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="20"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="32" t="s">
@@ -1717,7 +1732,7 @@
       <c r="P16" s="13"/>
       <c r="Q16" s="22"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>3</v>
       </c>
@@ -1764,7 +1779,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="9" t="s">
         <v>7</v>
@@ -1809,7 +1824,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="15"/>
       <c r="C19" s="32" t="s">
@@ -1832,7 +1847,7 @@
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
     </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1894,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="5" t="s">
         <v>8</v>
@@ -1920,7 +1935,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
         <v>8</v>
@@ -1965,7 +1980,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="5" t="s">
         <v>8</v>
@@ -2010,7 +2025,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="6"/>
@@ -2033,7 +2048,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="32" t="s">
@@ -2056,7 +2071,7 @@
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
     </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>3</v>
       </c>
@@ -2103,7 +2118,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="5" t="s">
         <v>9</v>
@@ -2148,7 +2163,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="5" t="s">
         <v>9</v>
@@ -2171,7 +2186,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="5" t="s">
         <v>9</v>
@@ -2194,7 +2209,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="20"/>
     </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="32" t="s">
@@ -2217,7 +2232,7 @@
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>3</v>
       </c>
@@ -2266,7 +2281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="5" t="s">
         <v>10</v>
@@ -2311,7 +2326,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="5" t="s">
         <v>10</v>
@@ -2356,7 +2371,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="5" t="s">
         <v>10</v>
@@ -2401,7 +2416,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="32" t="s">
@@ -2424,7 +2439,7 @@
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
     </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2486,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="5" t="s">
         <v>11</v>
@@ -2516,7 +2531,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="5" t="s">
         <v>11</v>
@@ -2561,7 +2576,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="5" t="s">
         <v>11</v>
@@ -2604,7 +2619,7 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="5" t="s">
         <v>11</v>
@@ -2649,7 +2664,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="32" t="s">
@@ -2672,7 +2687,7 @@
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
     </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
@@ -2719,7 +2734,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="5" t="s">
         <v>12</v>
@@ -2764,7 +2779,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="32" t="s">
@@ -2787,7 +2802,7 @@
       <c r="P44" s="13"/>
       <c r="Q44" s="24"/>
     </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>3</v>
       </c>
@@ -2834,7 +2849,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="23"/>
       <c r="C46" s="32" t="s">
@@ -2857,7 +2872,7 @@
       <c r="P46" s="13"/>
       <c r="Q46" s="17"/>
     </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>3</v>
       </c>
@@ -2902,7 +2917,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="26" t="s">
         <v>14</v>
@@ -2949,7 +2964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="27"/>
       <c r="C49" s="32" t="s">
@@ -2972,7 +2987,7 @@
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
     </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>3</v>
       </c>
@@ -3019,7 +3034,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="5" t="s">
         <v>15</v>
@@ -3064,7 +3079,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5" t="s">
         <v>15</v>
@@ -3109,7 +3124,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5" t="s">
         <v>15</v>
@@ -3154,7 +3169,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="32" t="s">
@@ -3177,7 +3192,7 @@
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
     </row>
-    <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>3</v>
       </c>
@@ -3224,7 +3239,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5" t="s">
         <v>16</v>
@@ -3269,7 +3284,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5" t="s">
         <v>16</v>
@@ -3314,7 +3329,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5" t="s">
         <v>16</v>
@@ -3357,7 +3372,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5" t="s">
         <v>16</v>
@@ -3402,7 +3417,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="5" t="s">
         <v>16</v>
@@ -3447,7 +3462,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="32" t="s">
@@ -3470,7 +3485,7 @@
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
     </row>
-    <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>3</v>
       </c>
@@ -3517,7 +3532,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="20"/>
     </row>
-    <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="5" t="s">
         <v>19</v>
@@ -3564,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="5" t="s">
         <v>19</v>
@@ -3611,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="32" t="s">
@@ -3632,7 +3647,7 @@
       <c r="P65" s="13"/>
       <c r="Q65" s="13"/>
     </row>
-    <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>3</v>
       </c>
@@ -3679,7 +3694,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="20"/>
     </row>
-    <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="5" t="s">
         <v>20</v>
@@ -3724,7 +3739,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="20"/>
     </row>
-    <row r="68" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="5" t="s">
         <v>20</v>
@@ -3769,7 +3784,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="6" t="s">
@@ -3812,7 +3827,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="32" t="s">
@@ -3833,7 +3848,7 @@
       <c r="P70" s="13"/>
       <c r="Q70" s="13"/>
     </row>
-    <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>17</v>
       </c>
@@ -3884,7 +3899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="5" t="s">
         <v>4</v>
@@ -3933,7 +3948,7 @@
         <v>127.4</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="5" t="s">
         <v>4</v>
@@ -3980,7 +3995,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="5" t="s">
         <v>4</v>
@@ -4027,7 +4042,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="32" t="s">
@@ -4050,7 +4065,7 @@
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
     </row>
-    <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>17</v>
       </c>
@@ -4066,7 +4081,9 @@
       <c r="E76" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="9"/>
+      <c r="F76" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="G76" s="8">
         <v>46</v>
       </c>
@@ -4097,7 +4114,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="20"/>
     </row>
-    <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="9" t="s">
         <v>5</v>
@@ -4144,7 +4161,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="9" t="s">
         <v>5</v>
@@ -4191,7 +4208,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="9" t="s">
         <v>5</v>
@@ -4232,7 +4249,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="20"/>
     </row>
-    <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="9"/>
       <c r="C80" s="6"/>
@@ -4255,7 +4272,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="13"/>
       <c r="B81" s="15"/>
       <c r="C81" s="32" t="s">
@@ -4278,7 +4295,7 @@
       <c r="P81" s="13"/>
       <c r="Q81" s="13"/>
     </row>
-    <row r="82" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>17</v>
       </c>
@@ -4325,7 +4342,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="5" t="s">
         <v>6</v>
@@ -4370,7 +4387,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="5" t="s">
         <v>6</v>
@@ -4415,7 +4432,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="32" t="s">
@@ -4438,7 +4455,7 @@
       <c r="P85" s="13"/>
       <c r="Q85" s="13"/>
     </row>
-    <row r="86" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>17</v>
       </c>
@@ -4485,7 +4502,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="9" t="s">
         <v>7</v>
@@ -4530,7 +4547,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="9" t="s">
         <v>7</v>
@@ -4575,7 +4592,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="9" t="s">
         <v>7</v>
@@ -4620,7 +4637,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="9" t="s">
         <v>7</v>
@@ -4665,7 +4682,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="13"/>
       <c r="B91" s="15"/>
       <c r="C91" s="32" t="s">
@@ -4688,7 +4705,7 @@
       <c r="P91" s="13"/>
       <c r="Q91" s="13"/>
     </row>
-    <row r="92" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>17</v>
       </c>
@@ -4735,7 +4752,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="5" t="s">
         <v>8</v>
@@ -4776,7 +4793,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="5" t="s">
         <v>8</v>
@@ -4821,7 +4838,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="5" t="s">
         <v>8</v>
@@ -4866,7 +4883,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="5" t="s">
         <v>8</v>
@@ -4911,7 +4928,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="5" t="s">
         <v>8</v>
@@ -4956,7 +4973,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="6"/>
@@ -4979,7 +4996,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="32" t="s">
@@ -5002,7 +5019,7 @@
       <c r="P99" s="13"/>
       <c r="Q99" s="13"/>
     </row>
-    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>17</v>
       </c>
@@ -5049,7 +5066,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="5" t="s">
         <v>9</v>
@@ -5094,7 +5111,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="5" t="s">
         <v>9</v>
@@ -5139,7 +5156,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="5" t="s">
         <v>9</v>
@@ -5184,7 +5201,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="5" t="s">
         <v>9</v>
@@ -5231,7 +5248,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="5" t="s">
         <v>9</v>
@@ -5276,7 +5293,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="32" t="s">
@@ -5299,7 +5316,7 @@
       <c r="P106" s="13"/>
       <c r="Q106" s="13"/>
     </row>
-    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>17</v>
       </c>
@@ -5346,7 +5363,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -5391,7 +5408,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -5436,7 +5453,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -5481,7 +5498,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="32" t="s">
@@ -5504,7 +5521,7 @@
       <c r="P111" s="13"/>
       <c r="Q111" s="13"/>
     </row>
-    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>17</v>
       </c>
@@ -5551,7 +5568,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="5" t="s">
         <v>11</v>
@@ -5596,7 +5613,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="32" t="s">
@@ -5619,7 +5636,7 @@
       <c r="P114" s="13"/>
       <c r="Q114" s="13"/>
     </row>
-    <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>17</v>
       </c>
@@ -5666,7 +5683,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="5" t="s">
         <v>12</v>
@@ -5711,7 +5728,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5" t="s">
         <v>12</v>
@@ -5756,7 +5773,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="5" t="s">
         <v>12</v>
@@ -5801,7 +5818,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="5" t="s">
         <v>12</v>
@@ -5846,7 +5863,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="5" t="s">
         <v>12</v>
@@ -5891,7 +5908,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="32" t="s">
@@ -5914,7 +5931,7 @@
       <c r="P121" s="13"/>
       <c r="Q121" s="13"/>
     </row>
-    <row r="122" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>17</v>
       </c>
@@ -5961,7 +5978,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="25" t="s">
         <v>13</v>
@@ -6006,7 +6023,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="25" t="s">
         <v>13</v>
@@ -6051,7 +6068,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="25" t="s">
         <v>13</v>
@@ -6096,7 +6113,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="13"/>
       <c r="B126" s="23"/>
       <c r="C126" s="32" t="s">
@@ -6119,7 +6136,7 @@
       <c r="P126" s="13"/>
       <c r="Q126" s="13"/>
     </row>
-    <row r="127" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>17</v>
       </c>
@@ -6166,7 +6183,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="26" t="s">
         <v>14</v>
@@ -6211,7 +6228,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="26" t="s">
         <v>14</v>
@@ -6256,7 +6273,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="13"/>
       <c r="B130" s="27"/>
       <c r="C130" s="32" t="s">
@@ -6279,7 +6296,7 @@
       <c r="P130" s="13"/>
       <c r="Q130" s="13"/>
     </row>
-    <row r="131" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>17</v>
       </c>
@@ -6326,7 +6343,7 @@
       <c r="P131" s="4"/>
       <c r="Q131" s="4"/>
     </row>
-    <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5" t="s">
         <v>15</v>
@@ -6371,7 +6388,7 @@
       <c r="P132" s="4"/>
       <c r="Q132" s="4"/>
     </row>
-    <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5" t="s">
         <v>15</v>
@@ -6414,7 +6431,7 @@
       <c r="P133" s="4"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="32" t="s">
@@ -6437,7 +6454,7 @@
       <c r="P134" s="13"/>
       <c r="Q134" s="13"/>
     </row>
-    <row r="135" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>17</v>
       </c>
@@ -6484,7 +6501,7 @@
       <c r="P135" s="4"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5" t="s">
         <v>16</v>
@@ -6527,7 +6544,7 @@
       <c r="P136" s="4"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="32" t="s">
@@ -6548,7 +6565,7 @@
       <c r="P137" s="13"/>
       <c r="Q137" s="13"/>
     </row>
-    <row r="138" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>17</v>
       </c>
@@ -6595,7 +6612,7 @@
       <c r="P138" s="4"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5" t="s">
         <v>19</v>
@@ -6640,7 +6657,7 @@
       <c r="P139" s="4"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="5" t="s">
         <v>19</v>
@@ -6685,7 +6702,7 @@
       <c r="P140" s="4"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="5" t="s">
         <v>19</v>
@@ -6730,7 +6747,7 @@
       <c r="P141" s="4"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5" t="s">
         <v>19</v>
@@ -6775,7 +6792,7 @@
       <c r="P142" s="4"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="32" t="s">
@@ -6796,7 +6813,7 @@
       <c r="P143" s="13"/>
       <c r="Q143" s="13"/>
     </row>
-    <row r="144" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>17</v>
       </c>
@@ -6845,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="5" t="s">
         <v>20</v>
@@ -6890,7 +6907,7 @@
       <c r="P145" s="4"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="5" t="s">
         <v>20</v>
@@ -6935,7 +6952,7 @@
       <c r="P146" s="4"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="32" t="s">
